--- a/Daily_Report/Top 7 broker List with its Turnover 2024-10-15.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-10-15.xlsx
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Sumeru Securities Pvt.Limited</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Sumeru Securities Pvt.Limited</t>
+    <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
-    <t>Premier Securites Company Limited</t>
+    <t>Linch Stock Market Limited</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>39</t>
+    <t>45</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>57</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>494,525,798.95</t>
-  </si>
-  <si>
-    <t>237,652,760.14</t>
-  </si>
-  <si>
-    <t>210,021,154.4</t>
-  </si>
-  <si>
-    <t>193,709,926.2</t>
-  </si>
-  <si>
-    <t>193,023,790.3</t>
-  </si>
-  <si>
-    <t>184,462,245.9</t>
-  </si>
-  <si>
-    <t>173,544,634.66</t>
-  </si>
-  <si>
-    <t>210,996,952.5</t>
-  </si>
-  <si>
-    <t>113,389,012.3</t>
-  </si>
-  <si>
-    <t>105,347,504.5</t>
-  </si>
-  <si>
-    <t>105,813,043.21</t>
-  </si>
-  <si>
-    <t>119,829,529.0</t>
-  </si>
-  <si>
-    <t>90,353,681.5</t>
-  </si>
-  <si>
-    <t>102,154,563.66</t>
-  </si>
-  <si>
-    <t>283,528,846.45</t>
-  </si>
-  <si>
-    <t>124,263,747.84</t>
-  </si>
-  <si>
-    <t>104,673,649.9</t>
-  </si>
-  <si>
-    <t>87,896,883.0</t>
-  </si>
-  <si>
-    <t>73,194,261.3</t>
-  </si>
-  <si>
-    <t>94,108,564.4</t>
-  </si>
-  <si>
-    <t>71,390,071.0</t>
+    <t>41</t>
+  </si>
+  <si>
+    <t>493,798,484.25</t>
+  </si>
+  <si>
+    <t>308,840,472.89</t>
+  </si>
+  <si>
+    <t>256,696,481.04</t>
+  </si>
+  <si>
+    <t>200,921,484.7</t>
+  </si>
+  <si>
+    <t>193,623,018.01</t>
+  </si>
+  <si>
+    <t>186,111,320.89</t>
+  </si>
+  <si>
+    <t>181,505,676.8</t>
+  </si>
+  <si>
+    <t>207,544,750.5</t>
+  </si>
+  <si>
+    <t>155,021,223.0</t>
+  </si>
+  <si>
+    <t>117,424,697.7</t>
+  </si>
+  <si>
+    <t>122,873,951.7</t>
+  </si>
+  <si>
+    <t>107,898,312.01</t>
+  </si>
+  <si>
+    <t>93,193,169.1</t>
+  </si>
+  <si>
+    <t>61,039,727.5</t>
+  </si>
+  <si>
+    <t>286,253,733.75</t>
+  </si>
+  <si>
+    <t>153,819,249.9</t>
+  </si>
+  <si>
+    <t>139,271,783.34</t>
+  </si>
+  <si>
+    <t>78,047,533.0</t>
+  </si>
+  <si>
+    <t>85,724,706.0</t>
+  </si>
+  <si>
+    <t>92,918,151.8</t>
+  </si>
+  <si>
+    <t>120,465,949.3</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,319 +182,319 @@
     <t>NRN</t>
   </si>
   <si>
-    <t>62,597,259.0</t>
+    <t>62,334,805.0</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>25,760,843.1</t>
+    <t>25,716,983.1</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>8,460,297.3</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>7,522,905.5</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>4,326,954.59</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>75,141,700.0</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>43,390,465.6</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>2,667,175.0</t>
+  </si>
+  <si>
+    <t>2,635,602.0</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>2,591,754.29</t>
+  </si>
+  <si>
+    <t>12,451,634.5</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>6,443,599.4</t>
+  </si>
+  <si>
+    <t>5,763,030.0</t>
+  </si>
+  <si>
+    <t>BPCL</t>
+  </si>
+  <si>
+    <t>5,250,642.5</t>
   </si>
   <si>
     <t>USHL</t>
   </si>
   <si>
-    <t>8,830,666.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>8,291,882.3</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>7,101,465.5</t>
-  </si>
-  <si>
-    <t>12,565,172.5</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>6,446,138.4</t>
-  </si>
-  <si>
-    <t>5,816,407.5</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>5,250,642.5</t>
+    <t>4,888,199.0</t>
+  </si>
+  <si>
+    <t>8,676,948.3</t>
+  </si>
+  <si>
+    <t>6,983,713.0</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>5,970,110.5</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>5,264,158.7</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>3,877,835.0</t>
+  </si>
+  <si>
+    <t>6,056,778.7</t>
+  </si>
+  <si>
+    <t>5,854,876.0</t>
+  </si>
+  <si>
+    <t>5,452,736.0</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>4,347,371.5</t>
+  </si>
+  <si>
+    <t>4,213,465.09</t>
+  </si>
+  <si>
+    <t>RURU</t>
+  </si>
+  <si>
+    <t>8,677,669.6</t>
+  </si>
+  <si>
+    <t>7,602,800.0</t>
+  </si>
+  <si>
+    <t>5,840,141.0</t>
+  </si>
+  <si>
+    <t>5,039,550.0</t>
+  </si>
+  <si>
+    <t>4,165,118.2</t>
+  </si>
+  <si>
+    <t>10,274,781.6</t>
+  </si>
+  <si>
+    <t>6,765,895.0</t>
+  </si>
+  <si>
+    <t>4,024,190.0</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>2,284,000.0</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>1,955,099.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>63,734,535.0</t>
+  </si>
+  <si>
+    <t>29,971,887.2</t>
+  </si>
+  <si>
+    <t>19,687,738.7</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>8,942,057.5</t>
+  </si>
+  <si>
+    <t>8,190,062.2</t>
+  </si>
+  <si>
+    <t>75,082,700.0</t>
+  </si>
+  <si>
+    <t>45,773,529.0</t>
+  </si>
+  <si>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>3,062,263.7</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>2,906,346.4</t>
+  </si>
+  <si>
+    <t>1,851,716.0</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>11,259,777.7</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>11,093,236.2</t>
+  </si>
+  <si>
+    <t>ADBL</t>
+  </si>
+  <si>
+    <t>7,741,375.0</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>6,596,899.8</t>
+  </si>
+  <si>
+    <t>5,447,194.4</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>3,448,494.0</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>2,865,031.0</t>
+  </si>
+  <si>
+    <t>CZBIL</t>
+  </si>
+  <si>
+    <t>2,776,464.4</t>
+  </si>
+  <si>
+    <t>2,420,040.1</t>
+  </si>
+  <si>
+    <t>SAPDBL</t>
+  </si>
+  <si>
+    <t>2,176,570.0</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>4,843,762.5</t>
+  </si>
+  <si>
+    <t>3,953,627.1</t>
+  </si>
+  <si>
+    <t>3,800,738.0</t>
   </si>
   <si>
     <t>JFL</t>
   </si>
   <si>
-    <t>3,610,428.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>56,121,284.6</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>12,621,700.0</t>
-  </si>
-  <si>
-    <t>3,218,967.0</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>2,591,754.29</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>2,507,448.0</t>
-  </si>
-  <si>
-    <t>5,895,172.2</t>
-  </si>
-  <si>
-    <t>5,808,476.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>4,538,008.7</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>4,347,371.5</t>
-  </si>
-  <si>
-    <t>3,669,015.1</t>
-  </si>
-  <si>
-    <t>7,964,738.3</t>
-  </si>
-  <si>
-    <t>6,519,841.0</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>5,970,110.5</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>5,264,158.7</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>3,877,835.0</t>
-  </si>
-  <si>
-    <t>RURU</t>
-  </si>
-  <si>
-    <t>8,844,341.6</t>
-  </si>
-  <si>
-    <t>5,417,200.0</t>
-  </si>
-  <si>
-    <t>4,593,221.0</t>
-  </si>
-  <si>
-    <t>4,421,425.0</t>
-  </si>
-  <si>
-    <t>4,010,058.2</t>
+    <t>3,342,126.0</t>
   </si>
   <si>
     <t>SHEL</t>
   </si>
   <si>
-    <t>25,039,990.7</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>10,699,646.0</t>
-  </si>
-  <si>
-    <t>SBL</t>
-  </si>
-  <si>
-    <t>7,055,585.0</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>5,947,602.4</t>
-  </si>
-  <si>
-    <t>ADBL</t>
-  </si>
-  <si>
-    <t>4,433,490.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>63,734,535.0</t>
-  </si>
-  <si>
-    <t>29,971,887.2</t>
-  </si>
-  <si>
-    <t>19,007,197.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>8,942,057.5</t>
-  </si>
-  <si>
-    <t>8,190,062.2</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>11,093,236.2</t>
-  </si>
-  <si>
-    <t>7,812,796.0</t>
-  </si>
-  <si>
-    <t>6,427,030.0</t>
-  </si>
-  <si>
-    <t>5,293,311.2</t>
-  </si>
-  <si>
-    <t>4,891,949.4</t>
-  </si>
-  <si>
-    <t>58,343,968.0</t>
-  </si>
-  <si>
-    <t>12,562,700.0</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>3,194,093.7</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>2,906,346.4</t>
-  </si>
-  <si>
-    <t>2,151,530.0</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>4,843,762.5</t>
-  </si>
-  <si>
-    <t>4,000,327.1</t>
-  </si>
-  <si>
-    <t>3,622,138.0</t>
-  </si>
-  <si>
-    <t>3,342,126.0</t>
-  </si>
-  <si>
     <t>3,151,048.5</t>
   </si>
   <si>
-    <t>2,865,031.0</t>
-  </si>
-  <si>
-    <t>2,597,816.4</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>2,123,600.4</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>2,098,130.0</t>
+    <t>6,323,327.0</t>
+  </si>
+  <si>
+    <t>4,592,507.59</t>
+  </si>
+  <si>
+    <t>3,960,339.2</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>3,821,655.4</t>
+  </si>
+  <si>
+    <t>3,233,050.0</t>
+  </si>
+  <si>
+    <t>49,553,485.0</t>
   </si>
   <si>
     <t>SANIMA</t>
   </si>
   <si>
-    <t>1,919,054.8</t>
-  </si>
-  <si>
-    <t>6,379,127.0</t>
-  </si>
-  <si>
-    <t>4,592,507.59</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>3,821,655.4</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>3,301,661.8</t>
-  </si>
-  <si>
-    <t>3,204,339.2</t>
-  </si>
-  <si>
-    <t>21,057,589.0</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>6,567,897.6</t>
-  </si>
-  <si>
-    <t>4,924,345.5</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>4,182,716.5</t>
-  </si>
-  <si>
-    <t>3,319,295.8</t>
+    <t>13,744,772.6</t>
+  </si>
+  <si>
+    <t>12,483,860.0</t>
+  </si>
+  <si>
+    <t>5,192,384.2</t>
+  </si>
+  <si>
+    <t>3,903,400.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -512,103 +512,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>180,501,304.1</t>
-  </si>
-  <si>
-    <t>112,359,442.6</t>
-  </si>
-  <si>
-    <t>109,373,399.1</t>
-  </si>
-  <si>
-    <t>100,264,699.6</t>
-  </si>
-  <si>
-    <t>84,113,583.3</t>
+    <t>180,534,520.6</t>
+  </si>
+  <si>
+    <t>136,541,001.9</t>
+  </si>
+  <si>
+    <t>107,565,421.6</t>
+  </si>
+  <si>
+    <t>87,002,979.7</t>
+  </si>
+  <si>
+    <t>84,113,794.2</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>698,257,905.9</t>
+    <t>730,926,788.6</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>667,006,504.29</t>
+    <t>658,181,943.1</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>559,875,003.79</t>
+    <t>587,257,925.6</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>343,510,315.89</t>
+    <t>357,721,665.2</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>231,789,455.5</t>
+    <t>220,555,285.6</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>129,164,021.9</t>
+    <t>135,449,401.4</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>119,503,789.3</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>79,253,864.2</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>123,228,525.1</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>119,454,280.4</t>
+    <t>57,685,939.8</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>58,374,161.7</t>
+    <t>55,688,368.0</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>48,468,517.5</t>
+    <t>50,910,211.7</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>37,361,030.0</t>
+    <t>37,231,723.5</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>26,162,170.3</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>14,968,614.2</t>
+    <t>25,261,934.3</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,280,632.74</t>
+    <t>4,288,974.74</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -626,208 +626,208 @@
     <t>100%</t>
   </si>
   <si>
-    <t>66,972,962.5</t>
-  </si>
-  <si>
-    <t>60,808,447.0</t>
-  </si>
-  <si>
-    <t>33,588,078.1</t>
-  </si>
-  <si>
-    <t>25,037,235.6</t>
-  </si>
-  <si>
-    <t>8,688,537.19</t>
-  </si>
-  <si>
-    <t>33,197,418.5</t>
-  </si>
-  <si>
-    <t>26,750,132.8</t>
-  </si>
-  <si>
-    <t>26,431,535.4</t>
-  </si>
-  <si>
-    <t>10,028,239.0</t>
-  </si>
-  <si>
-    <t>4,368,689.0</t>
-  </si>
-  <si>
-    <t>56,624,965.0</t>
-  </si>
-  <si>
-    <t>10,568,670.5</t>
-  </si>
-  <si>
-    <t>8,748,755.3</t>
-  </si>
-  <si>
-    <t>7,700,599.5</t>
-  </si>
-  <si>
-    <t>28,836,155.4</t>
-  </si>
-  <si>
-    <t>22,858,149.1</t>
-  </si>
-  <si>
-    <t>15,933,013.2</t>
-  </si>
-  <si>
-    <t>12,141,900.8</t>
+    <t>66,707,619.5</t>
+  </si>
+  <si>
+    <t>60,458,405.6</t>
+  </si>
+  <si>
+    <t>30,206,696.0</t>
+  </si>
+  <si>
+    <t>25,228,405.1</t>
+  </si>
+  <si>
+    <t>9,546,637.19</t>
+  </si>
+  <si>
+    <t>43,894,146.0</t>
+  </si>
+  <si>
+    <t>10,562,999.5</t>
+  </si>
+  <si>
+    <t>9,554,385.3</t>
+  </si>
+  <si>
+    <t>7,045,154.5</t>
+  </si>
+  <si>
+    <t>32,820,547.5</t>
+  </si>
+  <si>
+    <t>30,071,231.8</t>
+  </si>
+  <si>
+    <t>27,145,359.8</t>
+  </si>
+  <si>
+    <t>10,149,170.0</t>
+  </si>
+  <si>
+    <t>4,422,493.0</t>
+  </si>
+  <si>
+    <t>28,882,585.2</t>
+  </si>
+  <si>
+    <t>25,349,924.9</t>
+  </si>
+  <si>
+    <t>24,024,753.2</t>
+  </si>
+  <si>
+    <t>12,564,235.9</t>
+  </si>
+  <si>
+    <t>6,154,610.5</t>
+  </si>
+  <si>
+    <t>28,166,059.2</t>
+  </si>
+  <si>
+    <t>24,555,925.1</t>
+  </si>
+  <si>
+    <t>17,410,259.2</t>
+  </si>
+  <si>
+    <t>11,630,715.8</t>
   </si>
   <si>
     <t>4,927,440.8</t>
   </si>
   <si>
-    <t>28,765,691.0</t>
-  </si>
-  <si>
-    <t>25,848,892.9</t>
-  </si>
-  <si>
-    <t>22,408,121.2</t>
-  </si>
-  <si>
-    <t>11,184,825.9</t>
-  </si>
-  <si>
-    <t>6,154,610.5</t>
-  </si>
-  <si>
-    <t>28,282,811.4</t>
-  </si>
-  <si>
-    <t>21,694,087.9</t>
-  </si>
-  <si>
-    <t>20,036,992.2</t>
-  </si>
-  <si>
-    <t>8,124,213.1</t>
-  </si>
-  <si>
-    <t>3,046,012.9</t>
-  </si>
-  <si>
-    <t>34,236,535.79</t>
-  </si>
-  <si>
-    <t>27,271,555.3</t>
-  </si>
-  <si>
-    <t>13,486,435.5</t>
-  </si>
-  <si>
-    <t>10,077,167.6</t>
-  </si>
-  <si>
-    <t>6,776,260.4</t>
-  </si>
-  <si>
-    <t>80,796,540.59</t>
-  </si>
-  <si>
-    <t>65,455,441.5</t>
-  </si>
-  <si>
-    <t>57,971,427.5</t>
-  </si>
-  <si>
-    <t>28,567,749.0</t>
-  </si>
-  <si>
-    <t>26,217,651.2</t>
-  </si>
-  <si>
-    <t>35,524,708.29</t>
-  </si>
-  <si>
-    <t>22,823,976.9</t>
-  </si>
-  <si>
-    <t>18,916,800.2</t>
-  </si>
-  <si>
-    <t>18,523,153.8</t>
-  </si>
-  <si>
-    <t>11,114,546.2</t>
-  </si>
-  <si>
-    <t>61,171,927.4</t>
-  </si>
-  <si>
-    <t>9,392,817.5</t>
-  </si>
-  <si>
-    <t>6,271,227.8</t>
+    <t>27,812,510.4</t>
+  </si>
+  <si>
+    <t>24,772,127.9</t>
+  </si>
+  <si>
+    <t>21,102,476.2</t>
+  </si>
+  <si>
+    <t>7,981,017.5</t>
+  </si>
+  <si>
+    <t>2,686,721.9</t>
+  </si>
+  <si>
+    <t>19,828,794.1</t>
+  </si>
+  <si>
+    <t>15,836,730.9</t>
+  </si>
+  <si>
+    <t>9,630,969.8</t>
+  </si>
+  <si>
+    <t>7,364,388.7</t>
+  </si>
+  <si>
+    <t>2,475,569.1</t>
+  </si>
+  <si>
+    <t>80,023,328.09</t>
+  </si>
+  <si>
+    <t>65,621,566.5</t>
+  </si>
+  <si>
+    <t>60,821,515.2</t>
+  </si>
+  <si>
+    <t>28,463,773.0</t>
+  </si>
+  <si>
+    <t>25,743,287.2</t>
+  </si>
+  <si>
+    <t>48,301,674.4</t>
+  </si>
+  <si>
+    <t>9,165,787.5</t>
+  </si>
+  <si>
+    <t>6,027,142.8</t>
   </si>
   <si>
     <t>4,319,499.59</t>
   </si>
   <si>
-    <t>21,255,979.8</t>
-  </si>
-  <si>
-    <t>19,199,150.39</t>
-  </si>
-  <si>
-    <t>14,373,156.8</t>
-  </si>
-  <si>
-    <t>9,176,276.1</t>
+    <t>46,194,279.8</t>
+  </si>
+  <si>
+    <t>22,277,561.4</t>
+  </si>
+  <si>
+    <t>18,508,424.3</t>
+  </si>
+  <si>
+    <t>18,358,120.2</t>
+  </si>
+  <si>
+    <t>12,785,949.0</t>
+  </si>
+  <si>
+    <t>18,055,560.1</t>
+  </si>
+  <si>
+    <t>17,199,871.1</t>
+  </si>
+  <si>
+    <t>16,066,665.3</t>
+  </si>
+  <si>
+    <t>10,041,450.0</t>
+  </si>
+  <si>
+    <t>7,828,061.7</t>
+  </si>
+  <si>
+    <t>19,718,617.2</t>
+  </si>
+  <si>
+    <t>19,277,387.89</t>
+  </si>
+  <si>
+    <t>14,065,576.1</t>
+  </si>
+  <si>
+    <t>8,171,137.1</t>
   </si>
   <si>
     <t>7,848,176.0</t>
   </si>
   <si>
-    <t>17,674,165.89</t>
-  </si>
-  <si>
-    <t>15,847,527.1</t>
-  </si>
-  <si>
-    <t>14,839,316.3</t>
-  </si>
-  <si>
-    <t>9,741,358.0</t>
-  </si>
-  <si>
-    <t>6,213,386.7</t>
-  </si>
-  <si>
-    <t>29,311,144.2</t>
-  </si>
-  <si>
-    <t>22,670,138.1</t>
-  </si>
-  <si>
-    <t>12,510,400.6</t>
-  </si>
-  <si>
-    <t>9,038,063.6</t>
-  </si>
-  <si>
-    <t>6,609,999.7</t>
-  </si>
-  <si>
-    <t>30,965,076.1</t>
-  </si>
-  <si>
-    <t>13,729,377.2</t>
-  </si>
-  <si>
-    <t>13,152,322.1</t>
-  </si>
-  <si>
-    <t>4,887,100.3</t>
-  </si>
-  <si>
-    <t>2,223,778.0</t>
+    <t>29,753,565.2</t>
+  </si>
+  <si>
+    <t>21,733,459.1</t>
+  </si>
+  <si>
+    <t>12,165,975.1</t>
+  </si>
+  <si>
+    <t>9,654,393.1</t>
+  </si>
+  <si>
+    <t>6,521,249.7</t>
+  </si>
+  <si>
+    <t>70,656,287.7</t>
+  </si>
+  <si>
+    <t>20,901,724.8</t>
+  </si>
+  <si>
+    <t>9,655,401.3</t>
+  </si>
+  <si>
+    <t>9,473,469.8</t>
+  </si>
+  <si>
+    <t>3,009,023.8</t>
   </si>
 </sst>
 </file>
@@ -1636,61 +1636,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1265803707974577</v>
+        <v>0.1262353105329525</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.0528719821835771</v>
+        <v>0.2433026322438325</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.2672172941831997</v>
+        <v>0.04850722709385218</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0304329897560803</v>
+        <v>0.04318576638509183</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0.03128129476675747</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.04662623185970844</v>
+      </c>
+      <c r="T9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0.04126298777793713</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.04794662212231039</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>102</v>
-      </c>
       <c r="U9" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1442855940148026</v>
+        <v>0.05660859638743816</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1702,16 +1702,16 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0520920104768985</v>
+        <v>0.05207991502659215</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.02712418907401965</v>
+        <v>0.140494751845719</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>74</v>
@@ -1720,43 +1720,43 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.06009727941958212</v>
+        <v>0.02510201687959999</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02998543292873417</v>
+        <v>0.03475841824694619</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P10" s="18">
-        <v>0.03377739598764888</v>
+        <v>0.03023853289848842</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0293675270707522</v>
+        <v>0.04085081962362237</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="V10" s="18">
-        <v>0.06165356838004363</v>
+        <v>0.03727649250031611</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1768,25 +1768,25 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01785683581877766</v>
+        <v>0.01713309694105243</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02447439489688058</v>
+        <v>0.008636092850640108</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01532687032978236</v>
+        <v>0.02245075575890722</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>83</v>
@@ -1795,34 +1795,34 @@
         <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02342682581521593</v>
+        <v>0.029713649134706</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>91</v>
       </c>
       <c r="P11" s="18">
-        <v>0.03092940248826934</v>
+        <v>0.02816161041203471</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02490060216706924</v>
+        <v>0.0313798267174622</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="V11" s="18">
-        <v>0.04065573685883721</v>
+        <v>0.02217115227990489</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1834,16 +1834,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01676734018246511</v>
+        <v>0.01523476831125976</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02209375770307433</v>
+        <v>0.008533862078541067</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>77</v>
@@ -1852,7 +1852,7 @@
         <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01234044402529005</v>
+        <v>0.02045467268864435</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>85</v>
@@ -1861,7 +1861,7 @@
         <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02244268832815018</v>
+        <v>0.02620007864196317</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>92</v>
@@ -1870,25 +1870,25 @@
         <v>93</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02727207196490328</v>
+        <v>0.02245276178773059</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02396926795739507</v>
+        <v>0.02707814858134189</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0342713124589086</v>
+        <v>0.01258362845872157</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1900,16 +1900,16 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01436015171519496</v>
+        <v>0.008762591903399508</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01519203058223736</v>
+        <v>0.0083918868393884</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>79</v>
@@ -1918,43 +1918,43 @@
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01193902589081284</v>
+        <v>0.01904271916855101</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01894076969510813</v>
+        <v>0.01930025057195887</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>95</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.0200899329247085</v>
+        <v>0.02176117872402127</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02173918126408327</v>
+        <v>0.0223797143551411</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02554668433677522</v>
+        <v>0.0107715584133179</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1965,7 +1965,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1974,7 +1974,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1983,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1992,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2001,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2010,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2019,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2031,64 +2031,64 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1288801011703011</v>
+        <v>0.1290699283874928</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G16" s="12">
-        <v>0.04667833941194301</v>
+        <v>0.2431115951059664</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2778004347546811</v>
+        <v>0.04386416850897707</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>133</v>
-      </c>
       <c r="M16" s="16">
-        <v>0.02500523641080169</v>
+        <v>0.01716339098901751</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P16" s="18">
-        <v>0.01484289058642529</v>
+        <v>0.02501646007681708</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S16" s="16">
-        <v>0.03458229064097067</v>
+        <v>0.0339760470745227</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1213381735554947</v>
+        <v>0.2730134168453733</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2097,262 +2097,262 @@
         <v>56</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D17" s="10">
-        <v>0.06060732779490513</v>
+        <v>0.06069659619454371</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03287483804268683</v>
+        <v>0.1482109147489264</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J17" s="14">
-        <v>0.05981635533758403</v>
+        <v>0.04321538088506707</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>134</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02065112087061179</v>
+        <v>0.01425945564894584</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="P17" s="18">
-        <v>0.01345852962457343</v>
+        <v>0.02041919984841786</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02489673470900746</v>
+        <v>0.02467613242328022</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03784558141406963</v>
+        <v>0.07572640615062019</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.03986998609342127</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.009915357502355386</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.03015769818361356</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.01381865361061609</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.03843519941802219</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.02704378436932048</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.01520843797437959</v>
-      </c>
-      <c r="K18" s="15" t="s">
+      <c r="O18" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.01962957730471748</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.01869877331982078</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="P18" s="18">
-        <v>0.0110017547406953</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="R18" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02071781887591123</v>
+        <v>0.02127941052080299</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02837509502755606</v>
+        <v>0.06877944657210854</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01808208493669327</v>
+        <v>0.01810871799977584</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02227329990563433</v>
+        <v>0.009410510133952072</v>
       </c>
       <c r="H19" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>130</v>
-      </c>
       <c r="J19" s="14">
-        <v>0.01383835075234688</v>
+        <v>0.02569922179405346</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M19" s="16">
-        <v>0.0172532511130938</v>
+        <v>0.0120447054411001</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01086980002174374</v>
+        <v>0.01726099528015512</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01789884853613831</v>
+        <v>0.02053424467420456</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>158</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02410167567666134</v>
+        <v>0.02860728265662708</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01656144576762126</v>
+        <v>0.01658583908462048</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02058444175913706</v>
+        <v>0.005995703809842211</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01024434898544677</v>
+        <v>0.02122037036865802</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01626684063977167</v>
+        <v>0.010832938066578</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P20" s="18">
-        <v>0.009942063602716437</v>
+        <v>0.01627414205390218</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01737124680644474</v>
+        <v>0.01737159235862476</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="U20" s="17" t="s">
         <v>159</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01912646741573428</v>
+        <v>0.02150566345261549</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>165</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>166</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>167</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>168</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C28" s="21" t="s">
         <v>169</v>
@@ -2422,7 +2422,7 @@
         <v>171</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2280146579757763</v>
+        <v>0.2386826132575573</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2433,7 +2433,7 @@
         <v>173</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2178095781809359</v>
+        <v>0.2149279361876228</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -2444,7 +2444,7 @@
         <v>175</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1828260108793183</v>
+        <v>0.191767846690768</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -2455,7 +2455,7 @@
         <v>177</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1121725748169425</v>
+        <v>0.1168132611917529</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -2466,7 +2466,7 @@
         <v>179</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07569036164381496</v>
+        <v>0.07202186697193778</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -2477,7 +2477,7 @@
         <v>181</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04217824105885885</v>
+        <v>0.0442307185816063</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -2488,7 +2488,7 @@
         <v>183</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04024001699962115</v>
+        <v>0.0390237123186273</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -2499,7 +2499,7 @@
         <v>185</v>
       </c>
       <c r="D38" s="22">
-        <v>0.03900754529093614</v>
+        <v>0.02588018350544768</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -2510,7 +2510,7 @@
         <v>187</v>
       </c>
       <c r="D39" s="22">
-        <v>0.0190619603475773</v>
+        <v>0.01883722292632651</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -2521,7 +2521,7 @@
         <v>189</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01582729296292158</v>
+        <v>0.01818492003521641</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -2532,7 +2532,7 @@
         <v>191</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01220016616366494</v>
+        <v>0.01662462309436755</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2543,7 +2543,7 @@
         <v>193</v>
       </c>
       <c r="D42" s="22">
-        <v>0.008543201963706563</v>
+        <v>0.01215794139668068</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2554,7 +2554,7 @@
         <v>195</v>
       </c>
       <c r="D43" s="22">
-        <v>0.004887969643229711</v>
+        <v>0.008249231781767974</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -2565,7 +2565,7 @@
         <v>197</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001397831663463891</v>
+        <v>0.001400555726107167</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -2972,43 +2972,43 @@
         <v>203</v>
       </c>
       <c r="D9" s="10">
-        <v>0.135428652341698</v>
+        <v>0.1350907741268548</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.2433026322438325</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.1396887563201184</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>178</v>
-      </c>
       <c r="I9" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J9" s="14">
-        <v>0.2696155306915121</v>
+        <v>0.1278574110834254</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>217</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1488625594164899</v>
+        <v>0.1437506060794105</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O9" s="17" t="s">
         <v>222</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1490266611970058</v>
+        <v>0.145468547538833</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>172</v>
@@ -3017,16 +3017,16 @@
         <v>227</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1533257456668535</v>
+        <v>0.1494401859355134</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="U9" s="17" t="s">
         <v>232</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1972779848081994</v>
+        <v>0.1092461373637874</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3038,43 +3038,43 @@
         <v>204</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1229631439433722</v>
+        <v>0.1224353810883533</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1125597396143922</v>
+        <v>0.1421256274730954</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="J10" s="14">
-        <v>0.06009727941958212</v>
+        <v>0.1171470355891405</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>218</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1180019503761495</v>
+        <v>0.1261683136467486</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>223</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1339155803532058</v>
+        <v>0.126823377470192</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>170</v>
@@ -3083,16 +3083,16 @@
         <v>228</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1176071981242206</v>
+        <v>0.1331038207681648</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="U10" s="17" t="s">
         <v>233</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1571443297767694</v>
+        <v>0.08725198671031319</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3104,43 +3104,43 @@
         <v>205</v>
       </c>
       <c r="D11" s="10">
-        <v>0.06791976914311804</v>
+        <v>0.06117211162743661</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G11" s="12">
-        <v>0.1112191391525574</v>
+        <v>0.0342021218942383</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>214</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05032193318903117</v>
+        <v>0.1057488583015287</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L11" s="15" t="s">
         <v>219</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08225191920587022</v>
+        <v>0.119572843271947</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>224</v>
       </c>
       <c r="P11" s="18">
-        <v>0.1160899450019763</v>
+        <v>0.08991833398186581</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>174</v>
@@ -3149,16 +3149,16 @@
         <v>229</v>
       </c>
       <c r="S11" s="16">
-        <v>0.1086238113508733</v>
+        <v>0.1133863114718241</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="U11" s="17" t="s">
         <v>234</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0777116245997576</v>
+        <v>0.05306153487756918</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3170,25 +3170,25 @@
         <v>206</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05062877539080917</v>
+        <v>0.05109048712111352</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.03093631223357708</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.04219702306041982</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>170</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>215</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04165654324200782</v>
+        <v>0.03953762809244937</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>176</v>
@@ -3197,7 +3197,7 @@
         <v>220</v>
       </c>
       <c r="M12" s="16">
-        <v>0.06268083952929199</v>
+        <v>0.06253306319510787</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>176</v>
@@ -3206,7 +3206,7 @@
         <v>225</v>
       </c>
       <c r="P12" s="18">
-        <v>0.05794532312631724</v>
+        <v>0.06006886949463474</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>176</v>
@@ -3215,82 +3215,82 @@
         <v>230</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04404268776172371</v>
+        <v>0.04288303076570127</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>235</v>
       </c>
       <c r="V12" s="18">
-        <v>0.05806671937592703</v>
+        <v>0.04057387531804184</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>207</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01756943160184545</v>
+        <v>0.01933306298924712</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01838265626465448</v>
+        <v>0.02281162968650538</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>216</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03666582788766921</v>
+        <v>0.01722849094807365</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="L13" s="15" t="s">
         <v>221</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02543721375774097</v>
+        <v>0.03063191827986726</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="O13" s="17" t="s">
         <v>226</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03188524321501731</v>
+        <v>0.02544863131792272</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
         <v>231</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01651293404316075</v>
+        <v>0.01443610139892355</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="U13" s="17" t="s">
         <v>236</v>
       </c>
       <c r="V13" s="18">
-        <v>0.03904621086832049</v>
+        <v>0.01363907258243947</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3301,7 +3301,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3310,7 +3310,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3319,7 +3319,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3328,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3337,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3346,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3355,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3370,25 +3370,25 @@
         <v>237</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1633818514050246</v>
+        <v>0.1620566499339148</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.2431115951059664</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.1494815725223329</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>178</v>
-      </c>
       <c r="I16" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2912655516762553</v>
+        <v>0.1799568097421707</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>172</v>
@@ -3397,16 +3397,16 @@
         <v>251</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1097309787674819</v>
+        <v>0.0898637600999173</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>256</v>
       </c>
       <c r="P16" s="18">
-        <v>0.09156470232260276</v>
+        <v>0.1018402533059453</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>170</v>
@@ -3415,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1589005059381639</v>
+        <v>0.1598697223581954</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>170</v>
@@ -3424,7 +3424,7 @@
         <v>266</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1784271588727893</v>
+        <v>0.3892786658009365</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3436,43 +3436,43 @@
         <v>238</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1323600136514172</v>
+        <v>0.1328913890848988</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1563968412120638</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.09603918290936118</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>194</v>
-      </c>
       <c r="I17" s="13" t="s">
-        <v>126</v>
+        <v>247</v>
       </c>
       <c r="J17" s="14">
-        <v>0.05981635533758403</v>
+        <v>0.08678561275847242</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>252</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09911288892437187</v>
+        <v>0.0856049373001672</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="O17" s="17" t="s">
         <v>257</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08210141908087895</v>
+        <v>0.09956144728104788</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>172</v>
@@ -3481,16 +3481,16 @@
         <v>262</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1228985258711956</v>
+        <v>0.1167766635307353</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="U17" s="17" t="s">
         <v>267</v>
       </c>
       <c r="V17" s="18">
-        <v>0.0791115048119921</v>
+        <v>0.1151574163877612</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3502,43 +3502,43 @@
         <v>239</v>
       </c>
       <c r="D18" s="10">
-        <v>0.1172262956211539</v>
+        <v>0.1231707207290805</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07959848725870557</v>
+        <v>0.0296780645811529</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>248</v>
       </c>
       <c r="J18" s="14">
-        <v>0.04472319717903617</v>
+        <v>0.07210236862232601</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>253</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07419938193780598</v>
+        <v>0.07996489436652068</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="O18" s="17" t="s">
         <v>258</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07687817277308952</v>
+        <v>0.07264413211074708</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>174</v>
@@ -3547,16 +3547,16 @@
         <v>263</v>
       </c>
       <c r="S18" s="16">
-        <v>0.06782092746925619</v>
+        <v>0.06536934476187473</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="U18" s="17" t="s">
         <v>268</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07578639423666064</v>
+        <v>0.05319613948294977</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3568,16 +3568,16 @@
         <v>240</v>
       </c>
       <c r="D19" s="10">
-        <v>0.05776796490831492</v>
+        <v>0.05764248758930855</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0779420941254295</v>
+        <v>0.01951539169528321</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>174</v>
@@ -3586,25 +3586,25 @@
         <v>249</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0298599815714564</v>
+        <v>0.07151683624809536</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="L19" s="15" t="s">
         <v>254</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04737122293904569</v>
+        <v>0.04997698486547168</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="O19" s="17" t="s">
         <v>259</v>
       </c>
       <c r="P19" s="18">
-        <v>0.05046713664082473</v>
+        <v>0.04220126916717096</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>176</v>
@@ -3613,16 +3613,16 @@
         <v>264</v>
       </c>
       <c r="S19" s="16">
-        <v>0.04899682076352731</v>
+        <v>0.05187429251113333</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>269</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0281604804987176</v>
+        <v>0.05219379342299447</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3634,43 +3634,43 @@
         <v>241</v>
       </c>
       <c r="D20" s="10">
-        <v>0.05301574003958242</v>
+        <v>0.05213318392238463</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G20" s="12">
-        <v>0.04676800805280982</v>
+        <v>0.01398618373893832</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>250</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02056697389527347</v>
+        <v>0.04980959983634374</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="L20" s="15" t="s">
         <v>255</v>
       </c>
       <c r="M20" s="16">
-        <v>0.04051509467559154</v>
+        <v>0.03896079959636094</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>260</v>
       </c>
       <c r="P20" s="18">
-        <v>0.03218974557666222</v>
+        <v>0.04053327998221094</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>178</v>
@@ -3679,16 +3679,16 @@
         <v>265</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03583388930211437</v>
+        <v>0.03503951112949197</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="U20" s="17" t="s">
         <v>270</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01281386776581549</v>
+        <v>0.01657812500991704</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report/Top 7 broker List with its Turnover 2024-10-15.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-10-15.xlsx
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Sumeru Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Sani Securities Company Limited</t>
+    <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
-    <t>Linch Stock Market Limited</t>
+    <t>Premier Securites Company Limited</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>39</t>
   </si>
   <si>
-    <t>42</t>
+    <t>34</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>57</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>493,798,484.25</t>
-  </si>
-  <si>
-    <t>308,840,472.89</t>
-  </si>
-  <si>
-    <t>256,696,481.04</t>
-  </si>
-  <si>
-    <t>200,921,484.7</t>
-  </si>
-  <si>
-    <t>193,623,018.01</t>
-  </si>
-  <si>
-    <t>186,111,320.89</t>
-  </si>
-  <si>
-    <t>181,505,676.8</t>
-  </si>
-  <si>
-    <t>207,544,750.5</t>
-  </si>
-  <si>
-    <t>155,021,223.0</t>
-  </si>
-  <si>
-    <t>117,424,697.7</t>
-  </si>
-  <si>
-    <t>122,873,951.7</t>
-  </si>
-  <si>
-    <t>107,898,312.01</t>
-  </si>
-  <si>
-    <t>93,193,169.1</t>
-  </si>
-  <si>
-    <t>61,039,727.5</t>
-  </si>
-  <si>
-    <t>286,253,733.75</t>
-  </si>
-  <si>
-    <t>153,819,249.9</t>
-  </si>
-  <si>
-    <t>139,271,783.34</t>
-  </si>
-  <si>
-    <t>78,047,533.0</t>
-  </si>
-  <si>
-    <t>85,724,706.0</t>
-  </si>
-  <si>
-    <t>92,918,151.8</t>
-  </si>
-  <si>
-    <t>120,465,949.3</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>494,525,798.95</t>
+  </si>
+  <si>
+    <t>237,652,760.14</t>
+  </si>
+  <si>
+    <t>210,021,154.4</t>
+  </si>
+  <si>
+    <t>193,709,926.2</t>
+  </si>
+  <si>
+    <t>193,023,790.3</t>
+  </si>
+  <si>
+    <t>184,462,245.9</t>
+  </si>
+  <si>
+    <t>173,544,634.66</t>
+  </si>
+  <si>
+    <t>210,996,952.5</t>
+  </si>
+  <si>
+    <t>113,389,012.3</t>
+  </si>
+  <si>
+    <t>105,347,504.5</t>
+  </si>
+  <si>
+    <t>105,813,043.21</t>
+  </si>
+  <si>
+    <t>119,829,529.0</t>
+  </si>
+  <si>
+    <t>90,353,681.5</t>
+  </si>
+  <si>
+    <t>102,154,563.66</t>
+  </si>
+  <si>
+    <t>283,528,846.45</t>
+  </si>
+  <si>
+    <t>124,263,747.84</t>
+  </si>
+  <si>
+    <t>104,673,649.9</t>
+  </si>
+  <si>
+    <t>87,896,883.0</t>
+  </si>
+  <si>
+    <t>73,194,261.3</t>
+  </si>
+  <si>
+    <t>94,108,564.4</t>
+  </si>
+  <si>
+    <t>71,390,071.0</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,319 +182,319 @@
     <t>NRN</t>
   </si>
   <si>
-    <t>62,334,805.0</t>
+    <t>62,597,259.0</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>25,716,983.1</t>
+    <t>25,760,843.1</t>
+  </si>
+  <si>
+    <t>USHL</t>
+  </si>
+  <si>
+    <t>8,830,666.0</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>8,460,297.3</t>
+    <t>8,291,882.3</t>
   </si>
   <si>
     <t>GFCL</t>
   </si>
   <si>
-    <t>7,522,905.5</t>
+    <t>7,101,465.5</t>
+  </si>
+  <si>
+    <t>12,565,172.5</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>6,446,138.4</t>
+  </si>
+  <si>
+    <t>5,816,407.5</t>
+  </si>
+  <si>
+    <t>BPCL</t>
+  </si>
+  <si>
+    <t>5,250,642.5</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>3,610,428.0</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>56,121,284.6</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>12,621,700.0</t>
+  </si>
+  <si>
+    <t>3,218,967.0</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>2,591,754.29</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>2,507,448.0</t>
+  </si>
+  <si>
+    <t>5,895,172.2</t>
+  </si>
+  <si>
+    <t>5,808,476.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>4,538,008.7</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>4,347,371.5</t>
+  </si>
+  <si>
+    <t>3,669,015.1</t>
+  </si>
+  <si>
+    <t>7,964,738.3</t>
+  </si>
+  <si>
+    <t>6,519,841.0</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>5,970,110.5</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>5,264,158.7</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>3,877,835.0</t>
+  </si>
+  <si>
+    <t>RURU</t>
+  </si>
+  <si>
+    <t>8,844,341.6</t>
+  </si>
+  <si>
+    <t>5,417,200.0</t>
+  </si>
+  <si>
+    <t>4,593,221.0</t>
+  </si>
+  <si>
+    <t>4,421,425.0</t>
+  </si>
+  <si>
+    <t>4,010,058.2</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>25,039,990.7</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>10,699,646.0</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>7,055,585.0</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>5,947,602.4</t>
+  </si>
+  <si>
+    <t>ADBL</t>
+  </si>
+  <si>
+    <t>4,433,490.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>63,734,535.0</t>
+  </si>
+  <si>
+    <t>29,971,887.2</t>
+  </si>
+  <si>
+    <t>19,007,197.7</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>8,942,057.5</t>
+  </si>
+  <si>
+    <t>8,190,062.2</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>11,093,236.2</t>
+  </si>
+  <si>
+    <t>7,812,796.0</t>
+  </si>
+  <si>
+    <t>6,427,030.0</t>
+  </si>
+  <si>
+    <t>5,293,311.2</t>
+  </si>
+  <si>
+    <t>4,891,949.4</t>
+  </si>
+  <si>
+    <t>58,343,968.0</t>
+  </si>
+  <si>
+    <t>12,562,700.0</t>
+  </si>
+  <si>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>3,194,093.7</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>2,906,346.4</t>
+  </si>
+  <si>
+    <t>2,151,530.0</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>4,843,762.5</t>
+  </si>
+  <si>
+    <t>4,000,327.1</t>
+  </si>
+  <si>
+    <t>3,622,138.0</t>
+  </si>
+  <si>
+    <t>3,342,126.0</t>
+  </si>
+  <si>
+    <t>3,151,048.5</t>
+  </si>
+  <si>
+    <t>2,865,031.0</t>
+  </si>
+  <si>
+    <t>2,597,816.4</t>
   </si>
   <si>
     <t>API</t>
   </si>
   <si>
-    <t>4,326,954.59</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>75,141,700.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>43,390,465.6</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>2,667,175.0</t>
-  </si>
-  <si>
-    <t>2,635,602.0</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>2,591,754.29</t>
-  </si>
-  <si>
-    <t>12,451,634.5</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>6,443,599.4</t>
-  </si>
-  <si>
-    <t>5,763,030.0</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>5,250,642.5</t>
-  </si>
-  <si>
-    <t>USHL</t>
-  </si>
-  <si>
-    <t>4,888,199.0</t>
-  </si>
-  <si>
-    <t>8,676,948.3</t>
-  </si>
-  <si>
-    <t>6,983,713.0</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>5,970,110.5</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>5,264,158.7</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>3,877,835.0</t>
-  </si>
-  <si>
-    <t>6,056,778.7</t>
-  </si>
-  <si>
-    <t>5,854,876.0</t>
-  </si>
-  <si>
-    <t>5,452,736.0</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>4,347,371.5</t>
-  </si>
-  <si>
-    <t>4,213,465.09</t>
-  </si>
-  <si>
-    <t>RURU</t>
-  </si>
-  <si>
-    <t>8,677,669.6</t>
-  </si>
-  <si>
-    <t>7,602,800.0</t>
-  </si>
-  <si>
-    <t>5,840,141.0</t>
-  </si>
-  <si>
-    <t>5,039,550.0</t>
-  </si>
-  <si>
-    <t>4,165,118.2</t>
-  </si>
-  <si>
-    <t>10,274,781.6</t>
-  </si>
-  <si>
-    <t>6,765,895.0</t>
-  </si>
-  <si>
-    <t>4,024,190.0</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>2,284,000.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>1,955,099.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>63,734,535.0</t>
-  </si>
-  <si>
-    <t>29,971,887.2</t>
-  </si>
-  <si>
-    <t>19,687,738.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>8,942,057.5</t>
-  </si>
-  <si>
-    <t>8,190,062.2</t>
-  </si>
-  <si>
-    <t>75,082,700.0</t>
-  </si>
-  <si>
-    <t>45,773,529.0</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>3,062,263.7</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>2,906,346.4</t>
-  </si>
-  <si>
-    <t>1,851,716.0</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>11,259,777.7</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>11,093,236.2</t>
-  </si>
-  <si>
-    <t>ADBL</t>
-  </si>
-  <si>
-    <t>7,741,375.0</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>6,596,899.8</t>
-  </si>
-  <si>
-    <t>5,447,194.4</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>3,448,494.0</t>
-  </si>
-  <si>
-    <t>SBL</t>
-  </si>
-  <si>
-    <t>2,865,031.0</t>
-  </si>
-  <si>
-    <t>CZBIL</t>
-  </si>
-  <si>
-    <t>2,776,464.4</t>
-  </si>
-  <si>
-    <t>2,420,040.1</t>
-  </si>
-  <si>
-    <t>SAPDBL</t>
-  </si>
-  <si>
-    <t>2,176,570.0</t>
-  </si>
-  <si>
-    <t>HEI</t>
-  </si>
-  <si>
-    <t>4,843,762.5</t>
-  </si>
-  <si>
-    <t>3,953,627.1</t>
-  </si>
-  <si>
-    <t>3,800,738.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>3,342,126.0</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>3,151,048.5</t>
-  </si>
-  <si>
-    <t>6,323,327.0</t>
+    <t>2,123,600.4</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>2,098,130.0</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>1,919,054.8</t>
+  </si>
+  <si>
+    <t>6,379,127.0</t>
   </si>
   <si>
     <t>4,592,507.59</t>
   </si>
   <si>
-    <t>3,960,339.2</t>
-  </si>
-  <si>
     <t>PROFL</t>
   </si>
   <si>
     <t>3,821,655.4</t>
   </si>
   <si>
-    <t>3,233,050.0</t>
-  </si>
-  <si>
-    <t>49,553,485.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>13,744,772.6</t>
-  </si>
-  <si>
-    <t>12,483,860.0</t>
-  </si>
-  <si>
-    <t>5,192,384.2</t>
-  </si>
-  <si>
-    <t>3,903,400.0</t>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>3,301,661.8</t>
+  </si>
+  <si>
+    <t>3,204,339.2</t>
+  </si>
+  <si>
+    <t>21,057,589.0</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>6,567,897.6</t>
+  </si>
+  <si>
+    <t>4,924,345.5</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>4,182,716.5</t>
+  </si>
+  <si>
+    <t>3,319,295.8</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -512,103 +512,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>180,534,520.6</t>
-  </si>
-  <si>
-    <t>136,541,001.9</t>
-  </si>
-  <si>
-    <t>107,565,421.6</t>
-  </si>
-  <si>
-    <t>87,002,979.7</t>
-  </si>
-  <si>
-    <t>84,113,794.2</t>
+    <t>180,501,304.1</t>
+  </si>
+  <si>
+    <t>112,359,442.6</t>
+  </si>
+  <si>
+    <t>109,373,399.1</t>
+  </si>
+  <si>
+    <t>100,264,699.6</t>
+  </si>
+  <si>
+    <t>84,113,583.3</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>730,926,788.6</t>
+    <t>698,257,905.9</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>658,181,943.1</t>
+    <t>667,006,504.29</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>587,257,925.6</t>
+    <t>559,875,003.79</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>357,721,665.2</t>
+    <t>343,510,315.89</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>220,555,285.6</t>
+    <t>231,789,455.5</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>135,449,401.4</t>
+    <t>129,164,021.9</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>123,228,525.1</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>119,503,789.3</t>
+    <t>119,454,280.4</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>58,374,161.7</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>48,468,517.5</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>37,361,030.0</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>26,162,170.3</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>79,253,864.2</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>57,685,939.8</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>55,688,368.0</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>50,910,211.7</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>37,231,723.5</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>25,261,934.3</t>
+    <t>14,968,614.2</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,288,974.74</t>
+    <t>4,280,632.74</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -626,208 +626,208 @@
     <t>100%</t>
   </si>
   <si>
-    <t>66,707,619.5</t>
-  </si>
-  <si>
-    <t>60,458,405.6</t>
-  </si>
-  <si>
-    <t>30,206,696.0</t>
-  </si>
-  <si>
-    <t>25,228,405.1</t>
-  </si>
-  <si>
-    <t>9,546,637.19</t>
-  </si>
-  <si>
-    <t>43,894,146.0</t>
-  </si>
-  <si>
-    <t>10,562,999.5</t>
-  </si>
-  <si>
-    <t>9,554,385.3</t>
-  </si>
-  <si>
-    <t>7,045,154.5</t>
-  </si>
-  <si>
-    <t>32,820,547.5</t>
-  </si>
-  <si>
-    <t>30,071,231.8</t>
-  </si>
-  <si>
-    <t>27,145,359.8</t>
-  </si>
-  <si>
-    <t>10,149,170.0</t>
-  </si>
-  <si>
-    <t>4,422,493.0</t>
-  </si>
-  <si>
-    <t>28,882,585.2</t>
-  </si>
-  <si>
-    <t>25,349,924.9</t>
-  </si>
-  <si>
-    <t>24,024,753.2</t>
-  </si>
-  <si>
-    <t>12,564,235.9</t>
+    <t>66,972,962.5</t>
+  </si>
+  <si>
+    <t>60,808,447.0</t>
+  </si>
+  <si>
+    <t>33,588,078.1</t>
+  </si>
+  <si>
+    <t>25,037,235.6</t>
+  </si>
+  <si>
+    <t>8,688,537.19</t>
+  </si>
+  <si>
+    <t>33,197,418.5</t>
+  </si>
+  <si>
+    <t>26,750,132.8</t>
+  </si>
+  <si>
+    <t>26,431,535.4</t>
+  </si>
+  <si>
+    <t>10,028,239.0</t>
+  </si>
+  <si>
+    <t>4,368,689.0</t>
+  </si>
+  <si>
+    <t>56,624,965.0</t>
+  </si>
+  <si>
+    <t>10,568,670.5</t>
+  </si>
+  <si>
+    <t>8,748,755.3</t>
+  </si>
+  <si>
+    <t>7,700,599.5</t>
+  </si>
+  <si>
+    <t>28,836,155.4</t>
+  </si>
+  <si>
+    <t>22,858,149.1</t>
+  </si>
+  <si>
+    <t>15,933,013.2</t>
+  </si>
+  <si>
+    <t>12,141,900.8</t>
+  </si>
+  <si>
+    <t>4,927,440.8</t>
+  </si>
+  <si>
+    <t>28,765,691.0</t>
+  </si>
+  <si>
+    <t>25,848,892.9</t>
+  </si>
+  <si>
+    <t>22,408,121.2</t>
+  </si>
+  <si>
+    <t>11,184,825.9</t>
   </si>
   <si>
     <t>6,154,610.5</t>
   </si>
   <si>
-    <t>28,166,059.2</t>
-  </si>
-  <si>
-    <t>24,555,925.1</t>
-  </si>
-  <si>
-    <t>17,410,259.2</t>
-  </si>
-  <si>
-    <t>11,630,715.8</t>
-  </si>
-  <si>
-    <t>4,927,440.8</t>
-  </si>
-  <si>
-    <t>27,812,510.4</t>
-  </si>
-  <si>
-    <t>24,772,127.9</t>
-  </si>
-  <si>
-    <t>21,102,476.2</t>
-  </si>
-  <si>
-    <t>7,981,017.5</t>
-  </si>
-  <si>
-    <t>2,686,721.9</t>
-  </si>
-  <si>
-    <t>19,828,794.1</t>
-  </si>
-  <si>
-    <t>15,836,730.9</t>
-  </si>
-  <si>
-    <t>9,630,969.8</t>
-  </si>
-  <si>
-    <t>7,364,388.7</t>
-  </si>
-  <si>
-    <t>2,475,569.1</t>
-  </si>
-  <si>
-    <t>80,023,328.09</t>
-  </si>
-  <si>
-    <t>65,621,566.5</t>
-  </si>
-  <si>
-    <t>60,821,515.2</t>
-  </si>
-  <si>
-    <t>28,463,773.0</t>
-  </si>
-  <si>
-    <t>25,743,287.2</t>
-  </si>
-  <si>
-    <t>48,301,674.4</t>
-  </si>
-  <si>
-    <t>9,165,787.5</t>
-  </si>
-  <si>
-    <t>6,027,142.8</t>
+    <t>28,282,811.4</t>
+  </si>
+  <si>
+    <t>21,694,087.9</t>
+  </si>
+  <si>
+    <t>20,036,992.2</t>
+  </si>
+  <si>
+    <t>8,124,213.1</t>
+  </si>
+  <si>
+    <t>3,046,012.9</t>
+  </si>
+  <si>
+    <t>34,236,535.79</t>
+  </si>
+  <si>
+    <t>27,271,555.3</t>
+  </si>
+  <si>
+    <t>13,486,435.5</t>
+  </si>
+  <si>
+    <t>10,077,167.6</t>
+  </si>
+  <si>
+    <t>6,776,260.4</t>
+  </si>
+  <si>
+    <t>80,796,540.59</t>
+  </si>
+  <si>
+    <t>65,455,441.5</t>
+  </si>
+  <si>
+    <t>57,971,427.5</t>
+  </si>
+  <si>
+    <t>28,567,749.0</t>
+  </si>
+  <si>
+    <t>26,217,651.2</t>
+  </si>
+  <si>
+    <t>35,524,708.29</t>
+  </si>
+  <si>
+    <t>22,823,976.9</t>
+  </si>
+  <si>
+    <t>18,916,800.2</t>
+  </si>
+  <si>
+    <t>18,523,153.8</t>
+  </si>
+  <si>
+    <t>11,114,546.2</t>
+  </si>
+  <si>
+    <t>61,171,927.4</t>
+  </si>
+  <si>
+    <t>9,392,817.5</t>
+  </si>
+  <si>
+    <t>6,271,227.8</t>
   </si>
   <si>
     <t>4,319,499.59</t>
   </si>
   <si>
-    <t>46,194,279.8</t>
-  </si>
-  <si>
-    <t>22,277,561.4</t>
-  </si>
-  <si>
-    <t>18,508,424.3</t>
-  </si>
-  <si>
-    <t>18,358,120.2</t>
-  </si>
-  <si>
-    <t>12,785,949.0</t>
-  </si>
-  <si>
-    <t>18,055,560.1</t>
-  </si>
-  <si>
-    <t>17,199,871.1</t>
-  </si>
-  <si>
-    <t>16,066,665.3</t>
-  </si>
-  <si>
-    <t>10,041,450.0</t>
-  </si>
-  <si>
-    <t>7,828,061.7</t>
-  </si>
-  <si>
-    <t>19,718,617.2</t>
-  </si>
-  <si>
-    <t>19,277,387.89</t>
-  </si>
-  <si>
-    <t>14,065,576.1</t>
-  </si>
-  <si>
-    <t>8,171,137.1</t>
+    <t>21,255,979.8</t>
+  </si>
+  <si>
+    <t>19,199,150.39</t>
+  </si>
+  <si>
+    <t>14,373,156.8</t>
+  </si>
+  <si>
+    <t>9,176,276.1</t>
   </si>
   <si>
     <t>7,848,176.0</t>
   </si>
   <si>
-    <t>29,753,565.2</t>
-  </si>
-  <si>
-    <t>21,733,459.1</t>
-  </si>
-  <si>
-    <t>12,165,975.1</t>
-  </si>
-  <si>
-    <t>9,654,393.1</t>
-  </si>
-  <si>
-    <t>6,521,249.7</t>
-  </si>
-  <si>
-    <t>70,656,287.7</t>
-  </si>
-  <si>
-    <t>20,901,724.8</t>
-  </si>
-  <si>
-    <t>9,655,401.3</t>
-  </si>
-  <si>
-    <t>9,473,469.8</t>
-  </si>
-  <si>
-    <t>3,009,023.8</t>
+    <t>17,674,165.89</t>
+  </si>
+  <si>
+    <t>15,847,527.1</t>
+  </si>
+  <si>
+    <t>14,839,316.3</t>
+  </si>
+  <si>
+    <t>9,741,358.0</t>
+  </si>
+  <si>
+    <t>6,213,386.7</t>
+  </si>
+  <si>
+    <t>29,311,144.2</t>
+  </si>
+  <si>
+    <t>22,670,138.1</t>
+  </si>
+  <si>
+    <t>12,510,400.6</t>
+  </si>
+  <si>
+    <t>9,038,063.6</t>
+  </si>
+  <si>
+    <t>6,609,999.7</t>
+  </si>
+  <si>
+    <t>30,965,076.1</t>
+  </si>
+  <si>
+    <t>13,729,377.2</t>
+  </si>
+  <si>
+    <t>13,152,322.1</t>
+  </si>
+  <si>
+    <t>4,887,100.3</t>
+  </si>
+  <si>
+    <t>2,223,778.0</t>
   </si>
 </sst>
 </file>
@@ -1636,61 +1636,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1262353105329525</v>
+        <v>0.1265803707974577</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.2433026322438325</v>
+        <v>0.0528719821835771</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.04850722709385218</v>
+        <v>0.2672172941831997</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.04318576638509183</v>
+        <v>0.0304329897560803</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P9" s="18">
-        <v>0.03128129476675747</v>
+        <v>0.04126298777793713</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="S9" s="16">
-        <v>0.04662623185970844</v>
+        <v>0.04794662212231039</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.05660859638743816</v>
+        <v>0.1442855940148026</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1702,16 +1702,16 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.05207991502659215</v>
+        <v>0.0520920104768985</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.140494751845719</v>
+        <v>0.02712418907401965</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>74</v>
@@ -1720,43 +1720,43 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02510201687959999</v>
+        <v>0.06009727941958212</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.03475841824694619</v>
+        <v>0.02998543292873417</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P10" s="18">
-        <v>0.03023853289848842</v>
+        <v>0.03377739598764888</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S10" s="16">
-        <v>0.04085081962362237</v>
+        <v>0.0293675270707522</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03727649250031611</v>
+        <v>0.06165356838004363</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1768,25 +1768,25 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01713309694105243</v>
+        <v>0.01785683581877766</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G11" s="12">
-        <v>0.008636092850640108</v>
+        <v>0.02447439489688058</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02245075575890722</v>
+        <v>0.01532687032978236</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>83</v>
@@ -1795,34 +1795,34 @@
         <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.029713649134706</v>
+        <v>0.02342682581521593</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>91</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02816161041203471</v>
+        <v>0.03092940248826934</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S11" s="16">
-        <v>0.0313798267174622</v>
+        <v>0.02490060216706924</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02217115227990489</v>
+        <v>0.04065573685883721</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1834,16 +1834,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01523476831125976</v>
+        <v>0.01676734018246511</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.008533862078541067</v>
+        <v>0.02209375770307433</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>77</v>
@@ -1852,7 +1852,7 @@
         <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02045467268864435</v>
+        <v>0.01234044402529005</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>85</v>
@@ -1861,7 +1861,7 @@
         <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02620007864196317</v>
+        <v>0.02244268832815018</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>92</v>
@@ -1870,25 +1870,25 @@
         <v>93</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02245276178773059</v>
+        <v>0.02727207196490328</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02707814858134189</v>
+        <v>0.02396926795739507</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01258362845872157</v>
+        <v>0.0342713124589086</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1900,16 +1900,16 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.008762591903399508</v>
+        <v>0.01436015171519496</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.0083918868393884</v>
+        <v>0.01519203058223736</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>79</v>
@@ -1918,43 +1918,43 @@
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01904271916855101</v>
+        <v>0.01193902589081284</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.01930025057195887</v>
+        <v>0.01894076969510813</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02176117872402127</v>
+        <v>0.0200899329247085</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0223797143551411</v>
+        <v>0.02173918126408327</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="V13" s="18">
-        <v>0.0107715584133179</v>
+        <v>0.02554668433677522</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1965,7 +1965,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1974,7 +1974,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1983,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1992,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2001,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2010,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2019,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2031,64 +2031,64 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1290699283874928</v>
+        <v>0.1288801011703011</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>64</v>
+        <v>119</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2431115951059664</v>
+        <v>0.04667833941194301</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J16" s="14">
-        <v>0.04386416850897707</v>
+        <v>0.2778004347546811</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M16" s="16">
-        <v>0.01716339098901751</v>
+        <v>0.02500523641080169</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P16" s="18">
-        <v>0.02501646007681708</v>
+        <v>0.01484289058642529</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="S16" s="16">
-        <v>0.0339760470745227</v>
+        <v>0.03458229064097067</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2730134168453733</v>
+        <v>0.1213381735554947</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2097,262 +2097,262 @@
         <v>56</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.06060732779490513</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="10">
-        <v>0.06069659619454371</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>66</v>
-      </c>
       <c r="F17" s="11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1482109147489264</v>
+        <v>0.03287483804268683</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J17" s="14">
-        <v>0.04321538088506707</v>
+        <v>0.05981635533758403</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>134</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01425945564894584</v>
+        <v>0.02065112087061179</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02041919984841786</v>
+        <v>0.01345852962457343</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02467613242328022</v>
+        <v>0.02489673470900746</v>
       </c>
       <c r="T17" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="U17" s="17" t="s">
-        <v>156</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.07572640615062019</v>
+        <v>0.03784558141406963</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03986998609342127</v>
+        <v>0.03843519941802219</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G18" s="12">
-        <v>0.009915357502355386</v>
+        <v>0.02704378436932048</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03015769818361356</v>
+        <v>0.01520843797437959</v>
       </c>
       <c r="K18" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="L18" s="15" t="s">
-        <v>136</v>
-      </c>
       <c r="M18" s="16">
-        <v>0.01381865361061609</v>
+        <v>0.01869877331982078</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01962957730471748</v>
+        <v>0.0110017547406953</v>
       </c>
       <c r="Q18" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.02071781887591123</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="R18" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.02127941052080299</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>92</v>
-      </c>
       <c r="U18" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V18" s="18">
-        <v>0.06877944657210854</v>
+        <v>0.02837509502755606</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01810871799977584</v>
+        <v>0.01808208493669327</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G19" s="12">
-        <v>0.009410510133952072</v>
+        <v>0.02227329990563433</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02569922179405346</v>
+        <v>0.01383835075234688</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M19" s="16">
-        <v>0.0120447054411001</v>
+        <v>0.0172532511130938</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01726099528015512</v>
+        <v>0.01086980002174374</v>
       </c>
       <c r="Q19" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="R19" s="15" t="s">
-        <v>152</v>
-      </c>
       <c r="S19" s="16">
-        <v>0.02053424467420456</v>
+        <v>0.01789884853613831</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>158</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02860728265662708</v>
+        <v>0.02410167567666134</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01658583908462048</v>
+        <v>0.01656144576762126</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.02058444175913706</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.005995703809842211</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>104</v>
-      </c>
       <c r="I20" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02122037036865802</v>
+        <v>0.01024434898544677</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M20" s="16">
-        <v>0.010832938066578</v>
+        <v>0.01626684063977167</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01627414205390218</v>
+        <v>0.009942063602716437</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01737159235862476</v>
+        <v>0.01737124680644474</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="U20" s="17" t="s">
         <v>159</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02150566345261549</v>
+        <v>0.01912646741573428</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>165</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>166</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>167</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>168</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="C28" s="21" t="s">
         <v>169</v>
@@ -2422,7 +2422,7 @@
         <v>171</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2386826132575573</v>
+        <v>0.2280146579757763</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2433,7 +2433,7 @@
         <v>173</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2149279361876228</v>
+        <v>0.2178095781809359</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -2444,7 +2444,7 @@
         <v>175</v>
       </c>
       <c r="D33" s="22">
-        <v>0.191767846690768</v>
+        <v>0.1828260108793183</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -2455,7 +2455,7 @@
         <v>177</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1168132611917529</v>
+        <v>0.1121725748169425</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -2466,7 +2466,7 @@
         <v>179</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07202186697193778</v>
+        <v>0.07569036164381496</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -2477,7 +2477,7 @@
         <v>181</v>
       </c>
       <c r="D36" s="22">
-        <v>0.0442307185816063</v>
+        <v>0.04217824105885885</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -2488,7 +2488,7 @@
         <v>183</v>
       </c>
       <c r="D37" s="22">
-        <v>0.0390237123186273</v>
+        <v>0.04024001699962115</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -2499,7 +2499,7 @@
         <v>185</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02588018350544768</v>
+        <v>0.03900754529093614</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -2510,7 +2510,7 @@
         <v>187</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01883722292632651</v>
+        <v>0.0190619603475773</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -2521,7 +2521,7 @@
         <v>189</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01818492003521641</v>
+        <v>0.01582729296292158</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -2532,7 +2532,7 @@
         <v>191</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01662462309436755</v>
+        <v>0.01220016616366494</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2543,7 +2543,7 @@
         <v>193</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01215794139668068</v>
+        <v>0.008543201963706563</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2554,7 +2554,7 @@
         <v>195</v>
       </c>
       <c r="D43" s="22">
-        <v>0.008249231781767974</v>
+        <v>0.004887969643229711</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -2565,7 +2565,7 @@
         <v>197</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001400555726107167</v>
+        <v>0.001397831663463891</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -2972,43 +2972,43 @@
         <v>203</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1350907741268548</v>
+        <v>0.135428652341698</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2433026322438325</v>
+        <v>0.1396887563201184</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0.2696155306915121</v>
+      </c>
+      <c r="K9" s="15" t="s">
         <v>172</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="J9" s="14">
-        <v>0.1278574110834254</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>174</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>217</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1437506060794105</v>
+        <v>0.1488625594164899</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O9" s="17" t="s">
         <v>222</v>
       </c>
       <c r="P9" s="18">
-        <v>0.145468547538833</v>
+        <v>0.1490266611970058</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>172</v>
@@ -3017,16 +3017,16 @@
         <v>227</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1494401859355134</v>
+        <v>0.1533257456668535</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="U9" s="17" t="s">
         <v>232</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1092461373637874</v>
+        <v>0.1972779848081994</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3038,43 +3038,43 @@
         <v>204</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1224353810883533</v>
+        <v>0.1229631439433722</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1421256274730954</v>
+        <v>0.1125597396143922</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>213</v>
+        <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1171470355891405</v>
+        <v>0.06009727941958212</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>218</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1261683136467486</v>
+        <v>0.1180019503761495</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>223</v>
       </c>
       <c r="P10" s="18">
-        <v>0.126823377470192</v>
+        <v>0.1339155803532058</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>170</v>
@@ -3083,16 +3083,16 @@
         <v>228</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1331038207681648</v>
+        <v>0.1176071981242206</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="U10" s="17" t="s">
         <v>233</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08725198671031319</v>
+        <v>0.1571443297767694</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3104,43 +3104,43 @@
         <v>205</v>
       </c>
       <c r="D11" s="10">
-        <v>0.06117211162743661</v>
+        <v>0.06791976914311804</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.1112191391525574</v>
+      </c>
+      <c r="H11" s="13" t="s">
         <v>172</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.0342021218942383</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>170</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>214</v>
       </c>
       <c r="J11" s="14">
-        <v>0.1057488583015287</v>
+        <v>0.05032193318903117</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L11" s="15" t="s">
         <v>219</v>
       </c>
       <c r="M11" s="16">
-        <v>0.119572843271947</v>
+        <v>0.08225191920587022</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>224</v>
       </c>
       <c r="P11" s="18">
-        <v>0.08991833398186581</v>
+        <v>0.1160899450019763</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>174</v>
@@ -3149,16 +3149,16 @@
         <v>229</v>
       </c>
       <c r="S11" s="16">
-        <v>0.1133863114718241</v>
+        <v>0.1086238113508733</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="U11" s="17" t="s">
         <v>234</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05306153487756918</v>
+        <v>0.0777116245997576</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3170,25 +3170,25 @@
         <v>206</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05109048712111352</v>
+        <v>0.05062877539080917</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.04219702306041982</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>170</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.03093631223357708</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>176</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>215</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03953762809244937</v>
+        <v>0.04165654324200782</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>176</v>
@@ -3197,7 +3197,7 @@
         <v>220</v>
       </c>
       <c r="M12" s="16">
-        <v>0.06253306319510787</v>
+        <v>0.06268083952929199</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>176</v>
@@ -3206,7 +3206,7 @@
         <v>225</v>
       </c>
       <c r="P12" s="18">
-        <v>0.06006886949463474</v>
+        <v>0.05794532312631724</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>176</v>
@@ -3215,82 +3215,82 @@
         <v>230</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04288303076570127</v>
+        <v>0.04404268776172371</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="U12" s="17" t="s">
         <v>235</v>
       </c>
       <c r="V12" s="18">
-        <v>0.04057387531804184</v>
+        <v>0.05806671937592703</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>207</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01933306298924712</v>
+        <v>0.01756943160184545</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.01838265626465448</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>174</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.02281162968650538</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>182</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>216</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01722849094807365</v>
+        <v>0.03666582788766921</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="L13" s="15" t="s">
         <v>221</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03063191827986726</v>
+        <v>0.02543721375774097</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="O13" s="17" t="s">
         <v>226</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02544863131792272</v>
+        <v>0.03188524321501731</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R13" s="15" t="s">
         <v>231</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01443610139892355</v>
+        <v>0.01651293404316075</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="U13" s="17" t="s">
         <v>236</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01363907258243947</v>
+        <v>0.03904621086832049</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3301,7 +3301,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3310,7 +3310,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3319,7 +3319,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3328,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3337,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3346,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3355,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3370,25 +3370,25 @@
         <v>237</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1620566499339148</v>
+        <v>0.1633818514050246</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2431115951059664</v>
+        <v>0.1494815725223329</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1799568097421707</v>
+        <v>0.2912655516762553</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>172</v>
@@ -3397,16 +3397,16 @@
         <v>251</v>
       </c>
       <c r="M16" s="16">
-        <v>0.0898637600999173</v>
+        <v>0.1097309787674819</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>256</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1018402533059453</v>
+        <v>0.09156470232260276</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>170</v>
@@ -3415,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1598697223581954</v>
+        <v>0.1589005059381639</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>170</v>
@@ -3424,7 +3424,7 @@
         <v>266</v>
       </c>
       <c r="V16" s="18">
-        <v>0.3892786658009365</v>
+        <v>0.1784271588727893</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3436,43 +3436,43 @@
         <v>238</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1328913890848988</v>
+        <v>0.1323600136514172</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1563968412120638</v>
+        <v>0.09603918290936118</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>247</v>
+        <v>126</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08678561275847242</v>
+        <v>0.05981635533758403</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>252</v>
       </c>
       <c r="M17" s="16">
-        <v>0.0856049373001672</v>
+        <v>0.09911288892437187</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O17" s="17" t="s">
         <v>257</v>
       </c>
       <c r="P17" s="18">
-        <v>0.09956144728104788</v>
+        <v>0.08210141908087895</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>172</v>
@@ -3481,16 +3481,16 @@
         <v>262</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1167766635307353</v>
+        <v>0.1228985258711956</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="U17" s="17" t="s">
         <v>267</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1151574163877612</v>
+        <v>0.0791115048119921</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3502,43 +3502,43 @@
         <v>239</v>
       </c>
       <c r="D18" s="10">
-        <v>0.1231707207290805</v>
+        <v>0.1172262956211539</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.07959848725870557</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>172</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.0296780645811529</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>170</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>248</v>
       </c>
       <c r="J18" s="14">
-        <v>0.07210236862232601</v>
+        <v>0.04472319717903617</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>253</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07996489436652068</v>
+        <v>0.07419938193780598</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="O18" s="17" t="s">
         <v>258</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07264413211074708</v>
+        <v>0.07687817277308952</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>174</v>
@@ -3547,16 +3547,16 @@
         <v>263</v>
       </c>
       <c r="S18" s="16">
-        <v>0.06536934476187473</v>
+        <v>0.06782092746925619</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="U18" s="17" t="s">
         <v>268</v>
       </c>
       <c r="V18" s="18">
-        <v>0.05319613948294977</v>
+        <v>0.07578639423666064</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3568,16 +3568,16 @@
         <v>240</v>
       </c>
       <c r="D19" s="10">
-        <v>0.05764248758930855</v>
+        <v>0.05776796490831492</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01951539169528321</v>
+        <v>0.0779420941254295</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>174</v>
@@ -3586,25 +3586,25 @@
         <v>249</v>
       </c>
       <c r="J19" s="14">
-        <v>0.07151683624809536</v>
+        <v>0.0298599815714564</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="L19" s="15" t="s">
         <v>254</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04997698486547168</v>
+        <v>0.04737122293904569</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="O19" s="17" t="s">
         <v>259</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04220126916717096</v>
+        <v>0.05046713664082473</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>176</v>
@@ -3613,16 +3613,16 @@
         <v>264</v>
       </c>
       <c r="S19" s="16">
-        <v>0.05187429251113333</v>
+        <v>0.04899682076352731</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>269</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05219379342299447</v>
+        <v>0.0281604804987176</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3634,43 +3634,43 @@
         <v>241</v>
       </c>
       <c r="D20" s="10">
-        <v>0.05213318392238463</v>
+        <v>0.05301574003958242</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01398618373893832</v>
+        <v>0.04676800805280982</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>250</v>
       </c>
       <c r="J20" s="14">
-        <v>0.04980959983634374</v>
+        <v>0.02056697389527347</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="L20" s="15" t="s">
         <v>255</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03896079959636094</v>
+        <v>0.04051509467559154</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>260</v>
       </c>
       <c r="P20" s="18">
-        <v>0.04053327998221094</v>
+        <v>0.03218974557666222</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>178</v>
@@ -3679,16 +3679,16 @@
         <v>265</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03503951112949197</v>
+        <v>0.03583388930211437</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="U20" s="17" t="s">
         <v>270</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01657812500991704</v>
+        <v>0.01281386776581549</v>
       </c>
     </row>
   </sheetData>
